--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_240_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_240_R24.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2515</v>
+        <v>2.9394</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9631</v>
+        <v>4.2148</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.7117</v>
+        <v>-1.2754</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2742</v>
+        <v>0.1038</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2348</v>
+        <v>0.3615</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.9606</v>
+        <v>-0.2576</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4766</v>
+        <v>3.4671</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3293</v>
+        <v>1.6672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1472</v>
+        <v>1.7999</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.2023</v>
+        <v>-3.3633</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0945</v>
+        <v>-1.3057</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1078</v>
+        <v>-2.0576</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5856</v>
+        <v>-0.4865</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1102</v>
+        <v>0.2992</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4753</v>
+        <v>-0.7857</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.0722</v>
+        <v>1.4665</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5361</v>
+        <v>1.6083</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1234</v>
+        <v>2.1029</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4324</v>
+        <v>5.1506</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.309</v>
+        <v>-3.0477</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1038</v>
+        <v>1.2742</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3615</v>
+        <v>3.2348</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2576</v>
+        <v>-1.9606</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4671</v>
+        <v>4.4766</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6672</v>
+        <v>4.3293</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7999</v>
+        <v>0.1472</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3633</v>
+        <v>-3.2023</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3057</v>
+        <v>-1.0945</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0576</v>
+        <v>-2.1078</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0154</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3025</v>
+        <v>1.4369</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4832</v>
+        <v>1.2977</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8193</v>
+        <v>0.1393</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4665</v>
+        <v>-1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2147</v>
+        <v>0.3834</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0077</v>
+        <v>0.2282</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2224</v>
+        <v>0.1551</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2093</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2951</v>
+        <v>-1.1264</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6229</v>
+        <v>-0.6901</v>
       </c>
       <c r="V4" t="n">
         <v>1.719</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0635</v>
+        <v>0.3822</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7419</v>
+        <v>1.2884</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8054</v>
+        <v>-0.9062</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0504</v>
@@ -844,13 +844,13 @@
         <v>2.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9203</v>
+        <v>-0.4747</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3339</v>
+        <v>0.2126</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5865</v>
+        <v>-0.6873</v>
       </c>
       <c r="V5" t="n">
         <v>0.2836</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0163</v>
+        <v>-0.6289</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2101</v>
+        <v>0.1437</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8062</v>
+        <v>-0.7726</v>
       </c>
       <c r="G6" t="n">
         <v>-3.7705</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9237</v>
+        <v>-1.5362</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1202</v>
+        <v>-0.7664</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8035</v>
+        <v>-0.7699</v>
       </c>
       <c r="V6" t="n">
         <v>2.8223</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0727</v>
+        <v>-1.7578</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2078</v>
+        <v>0.1579</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2805</v>
+        <v>-1.9157</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2905</v>
+        <v>-1.0679</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4274</v>
+        <v>-0.2616</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8631</v>
+        <v>-0.8063</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9226</v>
+        <v>1.2586</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1497</v>
+        <v>0.1176</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7729</v>
+        <v>1.141</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.2131</v>
+        <v>-2.3265</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5771</v>
+        <v>-0.3792</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.636</v>
+        <v>-1.9473</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5399</v>
+        <v>0.0059</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4629</v>
+        <v>0.0591</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.923</v>
+        <v>-0.0532</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4712</v>
+        <v>-2.05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5118</v>
+        <v>0.2641</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.983</v>
+        <v>-2.3141</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0679</v>
+        <v>-1.2905</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2616</v>
+        <v>-0.4274</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8063</v>
+        <v>-0.8631</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2586</v>
+        <v>1.9226</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1176</v>
+        <v>1.1497</v>
       </c>
       <c r="L8" t="n">
-        <v>1.141</v>
+        <v>0.7729</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3265</v>
+        <v>-3.2131</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3792</v>
+        <v>-1.5771</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9473</v>
+        <v>-1.636</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2926</v>
+        <v>-0.4373</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4129</v>
+        <v>0.5192</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1204</v>
+        <v>-0.9566</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9398</v>
+        <v>-2.2082</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7913</v>
+        <v>-2.1269</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1485</v>
+        <v>-0.0813</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9822</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9577</v>
+        <v>-0.226</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>-0.1571</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1362</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.672</v>
+        <v>-3.0061</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-1.3642</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7058</v>
+        <v>-1.6419</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4797</v>
+        <v>-2.8885</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1693</v>
+        <v>-0.8104</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.649</v>
+        <v>-2.078</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5746</v>
+        <v>-0.2757</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4306</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0368</v>
+        <v>-0.7063</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0543</v>
+        <v>-2.6127</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3684</v>
+        <v>-1.241</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6859</v>
+        <v>-1.3717</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9577</v>
+        <v>-0.4914</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4349</v>
+        <v>-0.4208</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0026</v>
+        <v>0.1418</v>
       </c>
       <c r="W10" t="n">
         <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1753</v>
+        <v>-3.6048</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2646</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9107</v>
+        <v>-2.6386</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8885</v>
+        <v>-0.4797</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8104</v>
+        <v>0.1693</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.078</v>
+        <v>-0.649</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2757</v>
+        <v>0.5746</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4306</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7063</v>
+        <v>0.0368</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6127</v>
+        <v>-1.0543</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.241</v>
+        <v>-0.3684</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3717</v>
+        <v>-0.6859</v>
       </c>
       <c r="P11" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6606</v>
+        <v>-0.8905</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9709</v>
+        <v>-0.5228</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6897</v>
+        <v>-0.3677</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1418</v>
+        <v>-2.0026</v>
       </c>
       <c r="W11" t="n">
         <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.821199999999999</v>
+        <v>-7.447900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.617099999999999</v>
+        <v>6.990400000000002</v>
       </c>
       <c r="F12" t="n">
         <v>-14.4384</v>
@@ -1375,7 +1375,7 @@
         <v>-22.7662</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.2628</v>
+        <v>-8.262799999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-14.5035</v>
@@ -1390,13 +1390,13 @@
         <v>16.2367</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.599499999999999</v>
+        <v>-4.2262</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06139999999999979</v>
+        <v>0.4348000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.6611</v>
+        <v>-4.661</v>
       </c>
       <c r="V12" t="n">
         <v>3.5002</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8097</v>
+        <v>5.57</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8493</v>
+        <v>5.6898</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0396</v>
+        <v>-0.1198</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2202</v>
+        <v>3.5786</v>
       </c>
       <c r="H13" t="n">
-        <v>1.528</v>
+        <v>-2.6783</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3078</v>
+        <v>6.257</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3284</v>
+        <v>5.4772</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1076</v>
+        <v>-0.89</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2208</v>
+        <v>6.3673</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1082</v>
+        <v>-1.8986</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5796</v>
+        <v>-1.7883</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5286</v>
+        <v>-0.1103</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>5.6617</v>
+        <v>-0.0266</v>
       </c>
       <c r="T13" t="n">
-        <v>5.4693</v>
+        <v>0.2126</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1924</v>
+        <v>-0.2392</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2836</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3335</v>
+        <v>4.3505</v>
       </c>
       <c r="E14" t="n">
-        <v>5.218</v>
+        <v>3.9499</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1154</v>
+        <v>0.4006</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5786</v>
+        <v>2.2728</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.6783</v>
+        <v>1.443</v>
       </c>
       <c r="I14" t="n">
-        <v>6.257</v>
+        <v>0.8298</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4772</v>
+        <v>2.8984</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.89</v>
+        <v>1.6973</v>
       </c>
       <c r="L14" t="n">
-        <v>6.3673</v>
+        <v>1.2011</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8986</v>
+        <v>-0.6256</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7883</v>
+        <v>-0.2543</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1103</v>
+        <v>-0.3713</v>
       </c>
       <c r="P14" t="n">
         <v>1.6237</v>
@@ -1546,22 +1546,22 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2631</v>
+        <v>0.454</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2592</v>
+        <v>0.3736</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0039</v>
+        <v>0.0804</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3943</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5591</v>
+        <v>2.2092</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3602</v>
+        <v>2.1928</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1989</v>
+        <v>0.0164</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2728</v>
+        <v>1.2202</v>
       </c>
       <c r="H16" t="n">
-        <v>1.443</v>
+        <v>1.528</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8298</v>
+        <v>-0.3078</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8984</v>
+        <v>2.3284</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6973</v>
+        <v>2.1076</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2011</v>
+        <v>0.2208</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6256</v>
+        <v>-1.1082</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2543</v>
+        <v>-0.5796</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3713</v>
+        <v>-0.5286</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3374</v>
+        <v>2.0612</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2161</v>
+        <v>1.8128</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1212</v>
+        <v>0.2484</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.7886</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8156</v>
+        <v>1.8328</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7725</v>
+        <v>1.8904</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0431</v>
+        <v>-0.0577</v>
       </c>
       <c r="G17" t="n">
         <v>2.5328</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8369</v>
+        <v>0.854</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5702</v>
+        <v>0.6882</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2667</v>
+        <v>0.1658</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3943</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0395</v>
+        <v>1.0661</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1216</v>
+        <v>0.5585</v>
       </c>
       <c r="G18" t="n">
         <v>2.3507</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2403</v>
+        <v>1.2669</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4208</v>
+        <v>1.0106</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1805</v>
+        <v>0.2563</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9329</v>
+        <v>-0.5797</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2723</v>
+        <v>-0.1544</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6605</v>
+        <v>-0.4253</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7084</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1523</v>
+        <v>-0.7991</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5548</v>
+        <v>-0.3196</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6603</v>
+        <v>-2.0477</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1515</v>
+        <v>-0.5054</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5087</v>
+        <v>-1.5423</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0889</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0523</v>
+        <v>-0.3352</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4876</v>
+        <v>0.1338</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4353</v>
+        <v>-0.4689</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0565</v>
+        <v>-3.2968</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9274</v>
+        <v>-1.6299</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1291</v>
+        <v>-1.6668</v>
       </c>
       <c r="G21" t="n">
         <v>1.3088</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0264</v>
+        <v>0.7861</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8883</v>
+        <v>0.4092</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9146</v>
+        <v>0.3769</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1444</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1309</v>
+        <v>-5.1537</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5822</v>
+        <v>-1.6386</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5487</v>
+        <v>-3.5151</v>
       </c>
       <c r="G22" t="n">
         <v>-2.841</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3104</v>
+        <v>-0.3332</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8962</v>
+        <v>0.0474</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4143</v>
+        <v>-0.3806</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8197</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.821200000000002</v>
+        <v>7.995100000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>14.9746</v>
+        <v>15.0923</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.153200000000001</v>
+        <v>-7.0971</v>
       </c>
       <c r="G23" t="n">
         <v>11.3609</v>
@@ -2248,13 +2248,13 @@
         <v>11.5978</v>
       </c>
       <c r="S23" t="n">
-        <v>4.599599999999999</v>
+        <v>4.7733</v>
       </c>
       <c r="T23" t="n">
-        <v>4.660799999999999</v>
+        <v>4.7789</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.06129999999999991</v>
+        <v>-0.005499999999999894</v>
       </c>
       <c r="V23" t="n">
         <v>-3.5002</v>
